--- a/imports/templates/quotes.xlsx
+++ b/imports/templates/quotes.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Optional. Reference exchange rate. NUMERIC(10,4). Never used for conversion.</t>
+          <t>Required. PEN per USD rate at transaction date. NUMERIC(10,4).</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
